--- a/rfp_output/2026-04-05/rfp_results_2026-04-05.xlsx
+++ b/rfp_output/2026-04-05/rfp_results_2026-04-05.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,18 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="000066CC"/>
       <sz val="9"/>
       <u val="single"/>
@@ -85,7 +97,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +112,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A237E"/>
       </patternFill>
     </fill>
     <fill>
@@ -144,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -155,37 +172,52 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,19 +585,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -602,436 +635,531 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>Dhwani
+Product</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Relevant
-Product</t>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Why Apply / BD Note</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>Scoring Reason</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>URL</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>✅ APPLY</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>RFP for For Multilingual Data Collection Services for AgriAI Collect</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>✅ APPLY</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>RFP for the Deployment of the AgriVaani Application</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>✅ APPLY</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>RFP for Agri AI Collect Deployment in Kharif 2026-2027</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>✅ APPLY</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>RFP for Data Collection for Foundational Numeracy Tool in UP</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Location: Uttar Pradesh</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>✅ APPLY</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>RFP - for an IVRS-based Treatment Literacy Programme for People with Diabe...</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>REACH</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Location: Thiruchirapalli district, Tamil Nadu</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>✅ APPLY</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>RFP -Empanelment of Technical Consultants for Panipat (Haryana), Amroha &amp; ...</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Foundation for MSME Clusters</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Location: Haryana, Uttar Pradesh, Punjab</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="8" t="n">
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>🤔 CONSIDER</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>RFP - Assessment of WASH Access among Affordable Housing Finance Borrowers</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Water.org</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="H11" s="11" t="inlineStr"/>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="8" t="n">
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>🤔 CONSIDER</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>RFP for Hiring a Survey Firm to Conduct the Technical Needs Assessment Sur...</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Location: Odisha</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="8" t="n">
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>🤔 CONSIDER</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>RFP - Hiring of Agency to provide Security Guard at Jhpiego State Office, ...</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Jhpiego</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Location: Bhubaneswar, Odisha</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="H13" s="11" t="inlineStr"/>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
           <t>View RFP →</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="8" t="n">
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>🤔 CONSIDER</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>RFQ - Advancing Rights and Choices: Documenting Good Practices and Policy ...</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>UNFPA</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+      <c r="H14" s="11" t="inlineStr"/>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>View RFP →</t>
         </is>
@@ -1039,20 +1167,20 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1064,22 +1192,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>All Scraped RFPs — 05 April 2026  (27 total)</t>
         </is>
@@ -1099,1034 +1229,1315 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>Dhwani
+Product</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Reason / Scoring Note</t>
-        </is>
-      </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
+          <t>BD Note / Why Apply</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Reason</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
           <t>URL</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="4" t="n">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>RFP for For Multilingual Data Collection Services for AgriAI Collect</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>RFP for the Deployment of the AgriVaani Application</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>RFP for Agri AI Collect Deployment in Kharif 2026-2027</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>RFP for Data Collection for Foundational Numeracy Tool in UP</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Location: Uttar Pradesh</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>RFP - for an IVRS-based Treatment Literacy Programme for People with Diabe...</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>REACH</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Location: Thiruchirapalli district, Tamil Nadu</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>APPLY</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>RFP -Empanelment of Technical Consultants for Panipat (Haryana), Amroha &amp; ...</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Foundation for MSME Clusters</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Location: Haryana, Uttar Pradesh, Punjab</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>RFP - Assessment of WASH Access among Affordable Housing Finance Borrowers</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Water.org</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
+      <c r="G9" s="11" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr"/>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="n">
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>RFP for Hiring a Survey Firm to Conduct the Technical Needs Assessment Sur...</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Location: Odisha</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
+      <c r="G10" s="11" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr"/>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="8" t="n">
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>RFP - Hiring of Agency to provide Security Guard at Jhpiego State Office, ...</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Jhpiego</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Location: Bhubaneswar, Odisha</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
+      <c r="G11" s="11" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="n">
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>CONSIDER</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>RFQ - Advancing Rights and Choices: Documenting Good Practices and Policy ...</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>UNFPA</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
+      <c r="G12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="13" t="n">
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>IFP - for Strengthening systems for multi-sectoral response to Gender-Base...</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>UNFPA</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="13" t="n">
+      <c r="G13" s="18" t="inlineStr"/>
+      <c r="H13" s="18" t="inlineStr"/>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>RFP - for hiring Ambulance vehicle only On Rent</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>MAMTA Health Institute for Mother and Child (MAMTA)</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>Location: Rajasthan</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr"/>
-      <c r="G14" s="13" t="inlineStr"/>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="13" t="n">
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="18" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>EOI for a study on Impact Evaluation and Value for Money Analysis of CINI’...</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Child in Need Institute (CINI)</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Location: Kolkata, West Bengal</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr"/>
-      <c r="G15" s="13" t="inlineStr"/>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="13" t="n">
+      <c r="G15" s="18" t="inlineStr"/>
+      <c r="H15" s="18" t="inlineStr"/>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>RFP - On-Call Taxi Services for Raipur (Chhattisgarh) Local &amp; Outstation T...</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Jhpiego</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>Location: Raipur, Chhattisgarh</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="inlineStr"/>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="13" t="n">
+      <c r="G16" s="18" t="inlineStr"/>
+      <c r="H16" s="18" t="inlineStr"/>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>RFQ - A Specialised Talent Management Agency to support the amplification ...</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>UNFPA</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr"/>
-      <c r="G17" s="13" t="inlineStr"/>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="13" t="n">
+      <c r="G17" s="18" t="inlineStr"/>
+      <c r="H17" s="18" t="inlineStr"/>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>ToR for External Independent Audit of Development Agency for Poor &amp; Tribal...</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Development Agency for Poor and Tribal Awakening (DAPTA)</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>Location: Bhawanipatna, Kalahandi, Odisha</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="13" t="n">
+      <c r="G18" s="18" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>RFP - Baseline Assessment of the Food Security Standard at Vikarabad In Te...</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>Location: Vikarabad, Telangana</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr"/>
-      <c r="G19" s="13" t="inlineStr"/>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="13" t="n">
+      <c r="G19" s="18" t="inlineStr"/>
+      <c r="H19" s="18" t="inlineStr"/>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>RFP - Consultancy Service for a Quasi-Experimental Baseline Study Under a ...</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>Location: Madhya Pradesh</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr"/>
-      <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="13" t="n">
+      <c r="G20" s="18" t="inlineStr"/>
+      <c r="H20" s="18" t="inlineStr"/>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>RFQ - Supply, Installation, Commissioning and Handover of Sewerage Pipe la...</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>WaterAid India</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>Location: Akarbarnagar Nagar Panchayat, Bhagalpur, Bihar</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr"/>
-      <c r="G21" s="13" t="inlineStr"/>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="13" t="n">
+      <c r="G21" s="18" t="inlineStr"/>
+      <c r="H21" s="18" t="inlineStr"/>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>EOI - External Independent Audit : Protecting the Rights of Children by Bu...</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>Regional Centre for Development Cooperation (RCDC)</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>Location: Odisha</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr"/>
-      <c r="G22" s="13" t="inlineStr"/>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="13" t="n">
+      <c r="G22" s="18" t="inlineStr"/>
+      <c r="H22" s="18" t="inlineStr"/>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>RFQ-Outsourced Manpower Services (Housekeeping, MTS, Security &amp; Drivers)</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI)</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr"/>
-      <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="13" t="n">
+      <c r="G23" s="18" t="inlineStr"/>
+      <c r="H23" s="18" t="inlineStr"/>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K23" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>RFP - for Hiring of a Nukkad Natak Agency for community-based activities u...</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>JSI R&amp;T India Foundation (JSI R&amp;T)</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>Location: Uttar Pradesh</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr"/>
-      <c r="G24" s="13" t="inlineStr"/>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="13" t="n">
+      <c r="G24" s="18" t="inlineStr"/>
+      <c r="H24" s="18" t="inlineStr"/>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K24" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>RFP - For Cab Hiring Services North East Region</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr"/>
-      <c r="G25" s="13" t="inlineStr"/>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="13" t="n">
+      <c r="G25" s="18" t="inlineStr"/>
+      <c r="H25" s="18" t="inlineStr"/>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>RFP - for a Travel Agency</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>The Humsafar Trust (HST)</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr"/>
-      <c r="G26" s="13" t="inlineStr"/>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="13" t="n">
+      <c r="G26" s="18" t="inlineStr"/>
+      <c r="H26" s="18" t="inlineStr"/>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>RFQ - Study on the Intersection of Megatrends and Child Marriage: Emerging...</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>UNFPA</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr"/>
-      <c r="G27" s="13" t="inlineStr"/>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="13" t="n">
+      <c r="G27" s="18" t="inlineStr"/>
+      <c r="H27" s="18" t="inlineStr"/>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>RFP - An Audio Visual Documentary On The Kalindi River System In The India...</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>AHEAD Initiatives</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>Location: Hingalganj, North 24 Parganas, West Bengal</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr"/>
-      <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>View →</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="13" t="n">
+      <c r="G28" s="18" t="inlineStr"/>
+      <c r="H28" s="18" t="inlineStr"/>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="inlineStr">
+        <is>
+          <t>View →</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>RFP - Development of a Standardised WASH BCC Tool – UL4BC India Package</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr"/>
-      <c r="G29" s="13" t="inlineStr"/>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="G29" s="18" t="inlineStr"/>
+      <c r="H29" s="18" t="inlineStr"/>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>Enable Claude API for detailed product mapping</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>Based on keyword matching (Claude API not configured)</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="inlineStr">
         <is>
           <t>View →</t>
         </is>
@@ -2134,36 +2545,36 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rfp_output/2026-04-05/rfp_results_2026-04-05.xlsx
+++ b/rfp_output/2026-04-05/rfp_results_2026-04-05.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>✅ 6 to Apply   🤔 4 to Consider   ⏭ 17 Skip   |   📋 27 total scraped     🟢 Green = Apply   🟡 Amber = Consider   ⬜ Grey = Skip</t>
+          <t>✅ 2 to Apply   🤔 7 to Consider   ⏭ 18 Skip   |   📋 27 total scraped     🟢 Green = Apply   🟡 Amber = Consider   ⬜ Grey = Skip</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     </row>
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -697,12 +697,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>mForm</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>RFP for For Multilingual Data Collection Services for AgriAI Collect</t>
+          <t>RFP for Data Collection for Foundational Numeracy Tool in UP</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -712,19 +712,19 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Location: India</t>
+          <t>Location: Uttar Pradesh</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Pitch mForm as the data collection backbone: offline-enabled forms for capturing student handwriting samples (photo/document uploads), geo-tagged school location data, and structured assessment responses; integrate with Wadhwani AI's ML pipeline via APIs for seamless data flow to training datasets.</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP requires large-scale handwriting data collection for AI/ML model training in education — mForm's offline-capable mobile data collection with geo-tagging, media capture, and integration capabilities is a strong fit for field-level numeracy assessment data gathering across UP schools.</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -735,7 +735,7 @@
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
@@ -744,17 +744,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>mForm | DaaS | Custom Dev</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>RFP for the Deployment of the AgriVaani Application</t>
+          <t>RFP - Assessment of WASH Access among Affordable Housing Finance Borrowers</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Lords Education and Health Society (LEHS)</t>
+          <t>Water.org</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -766,12 +766,12 @@
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Pitch mForm for geo-tagged, offline beneficiary surveys + DaaS (Superset/PowerBI) for real-time WASH access dashboards; position Dhwani's M&amp;E expertise and 10+ years in health/WASH sector as differentiator versus pure research firms.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>Water.org needs field-level WASH data collection and M&amp;E assessment across borrower households—a perfect use case for mForm's offline mobile data collection paired with analytics dashboards for impact measurement.</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
@@ -781,188 +781,188 @@
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>✅ APPLY</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="A7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>🤔 CONSIDER</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>mForm | Custom Dev</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>RFP for Agri AI Collect Deployment in Kharif 2026-2027</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Location: India</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Enable Claude API for detailed product mapping</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Position mForm as the field data collection backbone for Agri AI's Kharif deployment—offline-capable, geo-tagged, mobile-first forms can feed agricultural data to LEHS's AI models; couple with Custom Dev for AI integration layer if needed.</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>RFP seeks AI-powered agricultural data collection deployment, which aligns with Dhwani's mForm mobile data collection capability and custom dev expertise, but the emphasis on AI/ML is not Dhwani's primary strength and RFP details are incomplete.</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>View →</t>
         </is>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>✅ APPLY</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>RFP for Data Collection for Foundational Numeracy Tool in UP</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>🤔 CONSIDER</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>mForm</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>RFP for For Multilingual Data Collection Services for AgriAI Collect</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Location: Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Enable Claude API for detailed product mapping</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Location: India</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Pitch mForm's multilingual, offline-capable data collection with geo-tagging and media capture as the field-level data validation and collection layer for AgriAI's image-to-text model—positioning Dhwani as the infrastructure partner for ground truth data generation and farmer feedback loops.</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>RFP requires multilingual data collection services for an AI agriculture model, which aligns with Dhwani's mForm capabilities, but the core focus on image-to-text extraction and AI model development sits outside Dhwani's primary strengths in data collection infrastructure.</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>View →</t>
         </is>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>✅ APPLY</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>🤔 CONSIDER</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Custom Dev</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>RFP - for an IVRS-based Treatment Literacy Programme for People with Diabe...</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>REACH</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Location: Thiruchirapalli district, Tamil Nadu</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Enable Claude API for detailed product mapping</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>Position Dhwani's custom IVRS development experience + health information systems track record (HMIS, patient tracking); emphasize ability to integrate IVRS with mForm for offline beneficiary data capture and mGrant for program tracking if REACH scales to multiple districts.</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>REACH needs IVRS platform development for health treatment literacy delivery — Dhwani has IVRS capability and health sector expertise, but IVRS is not a core product and content adaptation/medical domain requires significant specialization.</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>View →</t>
         </is>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>✅ APPLY</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>RFP -Empanelment of Technical Consultants for Panipat (Haryana), Amroha &amp; ...</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Foundation for MSME Clusters</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Location: Haryana, Uttar Pradesh, Punjab</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Enable Claude API for detailed product mapping</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>🤔 CONSIDER</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Custom Dev | Tech Consulting | DaaS</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>IFP - for Strengthening systems for multi-sectoral response to Gender-Base...</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>UNFPA</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Location: India</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>Position mForm for case-level data collection and monitoring across multi-sectoral GBV response touchpoints, combined with Custom Dev for a case management/referral tracking MIS and DaaS dashboards for real-time GBV response metrics — but first clarify whether UNFPA wants technology as a core deliverable or as a supporting component.</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>UNFPA seeks to strengthen GBV response systems through one-stop centres and shelters, requiring M&amp;E, capacity building, and potentially case management systems — areas where Dhwani has relevant tech expertise, but the RFP lacks detailed technical specifications and seems primarily focused on institutional strengthening rather than technology deployment.</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>View →</t>
         </is>
@@ -970,7 +970,7 @@
     </row>
     <row r="11" ht="50" customHeight="1">
       <c r="A11" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
@@ -979,34 +979,34 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>mForm | DaaS | Tech Consulting</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>RFP - Assessment of WASH Access among Affordable Housing Finance Borrowers</t>
+          <t>RFP - Consultancy Service for a Quasi-Experimental Baseline Study Under a ...</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Water.org</t>
+          <t>Deutsche Welthungerhilfe</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Location: India</t>
+          <t>Location: Madhya Pradesh</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr"/>
       <c r="H11" s="14" t="inlineStr"/>
       <c r="I11" s="15" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Position mForm for offline-enabled baseline/endline survey data collection in remote Bundelkhand villages, paired with DaaS dashboards for quasi-experimental impact analysis and behaviour change tracking—but clarify whether Dhwani is being asked to design the study (skip) or implement the data infrastructure (apply).</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP requires baseline study design and quasi-experimental research methodology—not a core Dhwani strength—but WASH behaviour change programmes typically need robust data collection, M&amp;E systems, and impact dashboards that Dhwani can deliver if scoped correctly.</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr">
@@ -1026,34 +1026,34 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Custom Dev, Tech Consulting, mForm</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>RFP for Hiring a Survey Firm to Conduct the Technical Needs Assessment Sur...</t>
+          <t>RFP for the Deployment of the AgriVaani Application</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>EAII Advisors Pvt Ltd</t>
+          <t>Lords Education and Health Society (LEHS)</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Location: Odisha</t>
+          <t>Location: India</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr"/>
       <c r="H12" s="14" t="inlineStr"/>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Request clarification on whether AgriVaani deployment requires backend MIS integration, farmer beneficiary data collection via mForm, or M&amp;E dashboards to track adoption/impact—if yes, pitch Dhwani's agriculture tech stack and data systems; if it's purely AI model deployment, likely a weak fit.</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP seeks deployment of an existing AgriVaani application (likely an AI/ML tool) rather than development of a new system; while Dhwani has agriculture sector experience and tech deployment capability, the core need appears to be implementation/deployment of a pre-built AI solution, which is outside Dhwani's primary strengths unless significant MIS, data collection, or M&amp;E integration is required.</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr">
@@ -1073,34 +1073,34 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Custom Dev</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>RFP - Hiring of Agency to provide Security Guard at Jhpiego State Office, ...</t>
+          <t>RFP - Development of a Standardised WASH BCC Tool – UL4BC India Package</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Jhpiego</t>
+          <t>Deutsche Welthungerhilfe</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Location: Bhubaneswar, Odisha</t>
+          <t>Location: India</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="14" t="inlineStr"/>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>If the BCC tool requires digital platform features (mobile app for field workers, beneficiary tracking, survey/monitoring forms, or impact measurement dashboards), position mForm + DaaS to capture BCC programme data, monitor adoption, and measure behaviour change outcomes; otherwise, this is primarily a content/creative RFP outside Dhwani's core strength.</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP focuses on developing a standardised WASH BCC (Behaviour Change Communication) tool using sports/arts/music — primarily a content design and social mobilisation challenge rather than a core IT systems challenge, though digital delivery/tracking components could exist.</t>
         </is>
       </c>
       <c r="K13" s="16" t="inlineStr">
@@ -1109,48 +1109,48 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>🤔 CONSIDER</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>RFQ - Advancing Rights and Choices: Documenting Good Practices and Policy ...</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>UNFPA</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Location: India</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr"/>
-      <c r="H14" s="14" t="inlineStr"/>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>Enable Claude API for detailed product mapping</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>⏭ SKIP</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>EOI for a study on Impact Evaluation and Value for Money Analysis of CINI’...</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Child in Need Institute (CINI)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>Location: Kolkata, West Bengal</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>While CINI's maternal-child health programme could benefit from mForm for field data collection and DaaS for impact dashboards post-evaluation, this specific RFP is seeking an external research partner to conduct the study itself, not a tech vendor; revisit if CINI later needs to digitise their M&amp;E workflows or beneficiary tracking.</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>This RFP is for research/impact evaluation study design and execution, not for technology platform development, data systems, or MIS—Dhwani's core strengths lie in building and deploying digital solutions, not conducting independent research studies.</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>View →</t>
         </is>
@@ -1167,34 +1167,34 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>IFP - for Strengthening systems for multi-sectoral response to Gender-Base...</t>
+          <t>RFP for Hiring a Survey Firm to Conduct the Technical Needs Assessment Sur...</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>UNFPA</t>
+          <t>EAII Advisors Pvt Ltd</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Location: India</t>
+          <t>Location: Odisha</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr"/>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>While Dhwani has WASH sector experience and mForm could theoretically support data collection during the assessment phase, the RFP is explicitly seeking a survey firm for needs assessment work, not a technology vendor. Only pursue if EAII subsequently issues RFPs for M&amp;E platform, beneficiary tracking MIS, or WASH program dashboards post-assessment.</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for a survey firm to conduct a technical needs assessment in WASH/water sector—it's a field research/consulting engagement, not a software development or digital platform procurement that matches Dhwani's core product offerings.</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
@@ -1214,34 +1214,34 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>mForm</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>RFP - for hiring Ambulance vehicle only On Rent</t>
+          <t>RFP - Baseline Assessment of the Food Security Standard at Vikarabad In Te...</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA)</t>
+          <t>Deutsche Welthungerhilfe</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Location: Rajasthan</t>
+          <t>Location: Vikarabad, Telangana</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>While mForm could theoretically support field-level data collection for the baseline survey, this RFP is primarily seeking research/assessment services (survey design, data analysis, impact measurement methodology) — positioning Dhwani as a research consultant rather than a tech vendor would be a weak fit and misaligned with our core competency.</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for a baseline impact assessment and research study (food security standards validation), not for technology platform development, data collection infrastructure, or MIS — Dhwani's core strengths.</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -1252,7 +1252,7 @@
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>EOI for a study on Impact Evaluation and Value for Money Analysis of CINI’...</t>
+          <t>RFQ - Advancing Rights and Choices: Documenting Good Practices and Policy ...</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>Child in Need Institute (CINI)</t>
+          <t>UNFPA</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>Location: Kolkata, West Bengal</t>
+          <t>Location: India</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr"/>
       <c r="H17" s="20" t="inlineStr"/>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No primary tech scope detected; if a future phase involves M&amp;E platform or beneficiary tracking system for ASRH programmes, revisit with mForm + mGrant combo pitch.</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is a research/documentation study on policy pathways for married adolescent girls—primarily qualitative research and policy analysis work, not a technology procurement or system implementation.</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -1299,7 +1299,7 @@
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
@@ -1308,34 +1308,34 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>RFP - On-Call Taxi Services for Raipur (Chhattisgarh) Local &amp; Outstation T...</t>
+          <t>RFP -Empanelment of Technical Consultants for Panipat (Haryana), Amroha &amp; ...</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Jhpiego</t>
+          <t>Foundation for MSME Clusters</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Location: Raipur, Chhattisgarh</t>
+          <t>Location: Haryana, Uttar Pradesh, Punjab</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr"/>
       <c r="H18" s="20" t="inlineStr"/>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>The RFP document appears incomplete (cuts off mid-sentence); without clarity on whether MSME cluster management requires MIS, monitoring systems, or digital platforms, Dhwani cannot position its Tech Consulting or Custom Dev services appropriately—request full RFP document before deciding.</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP seeks empanelment of technical consultants for MSME cluster development across 3 states over 3 years, but the actual scope is unclear—no detailed description of required IT systems, data platforms, or digital solutions is provided in the excerpt.</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>RFQ - A Specialised Talent Management Agency to support the amplification ...</t>
+          <t>RFQ - Study on the Intersection of Megatrends and Child Marriage: Emerging...</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -1377,12 +1377,12 @@
       <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Unless the RFP scope expands to include M&amp;E dashboards, beneficiary tracking systems, or data collection for child marriage intervention programs post-study, this is a research consultancy play—outside Dhwani's core IT4D competency.</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for research/study services (literature review, expert convening, policy analysis on child marriage megatrends), not for technology development, data systems, or digital platforms that Dhwani specializes in.</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -1402,34 +1402,34 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>ToR for External Independent Audit of Development Agency for Poor &amp; Tribal...</t>
+          <t>RFP - for Hiring of a Nukkad Natak Agency for community-based activities u...</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Development Agency for Poor and Tribal Awakening (DAPTA)</t>
+          <t>JSI R&amp;T India Foundation (JSI R&amp;T)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>Location: Bhawanipatna, Kalahandi, Odisha</t>
+          <t>Location: Uttar Pradesh</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr"/>
       <c r="H20" s="20" t="inlineStr"/>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>This is a vendor hire for live performance/advocacy delivery, not a digital transformation or MIS need; Dhwani should not bid unless there's an embedded tech requirement (e.g., tracking beneficiary engagement data post-performances via mForm, which is not mentioned in the RFP).</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP is for hiring a Nukkad Natak (street theatre) agency to conduct community-based advocacy performances—a creative services role with no technology component, not a software/IT solutions procurement.</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -1449,34 +1449,34 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>RFP - Baseline Assessment of the Food Security Standard at Vikarabad In Te...</t>
+          <t>RFQ - A Specialised Talent Management Agency to support the amplification ...</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>Deutsche Welthungerhilfe</t>
+          <t>UNFPA</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Location: Vikarabad, Telangana</t>
+          <t>Location: India</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
       <c r="H21" s="20" t="inlineStr"/>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No BD action required; this RFP has zero tech/data/systems component and belongs to a marketing/communications agency, not an IT solutions provider.</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>UNFPA seeks a talent management and media communications agency for influencer relations and PR amplification — a creative services domain entirely outside Dhwani's ICT4D/software/MIS expertise.</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -1496,34 +1496,34 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>RFP - Consultancy Service for a Quasi-Experimental Baseline Study Under a ...</t>
+          <t>ToR for External Independent Audit of Development Agency for Poor &amp; Tribal...</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Deutsche Welthungerhilfe</t>
+          <t>Development Agency for Poor and Tribal Awakening (DAPTA)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Location: Madhya Pradesh</t>
+          <t>Location: Bhawanipatna, Kalahandi, Odisha</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
       <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No technology component. DAPTA needs an external audit firm (CA/audit practice), not a software or tech consulting vendor. This is outside Dhwani's service portfolio.</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for a Chartered Accountant-led financial audit of a BMZ-funded project's compliance and fund utilization — a statutory audit service, not an IT/software solution.</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -1543,34 +1543,34 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>RFQ - Supply, Installation, Commissioning and Handover of Sewerage Pipe la...</t>
+          <t>RFP - An Audio Visual Documentary On The Kalindi River System In The India...</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>WaterAid India</t>
+          <t>AHEAD Initiatives</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Location: Akarbarnagar Nagar Panchayat, Bhagalpur, Bihar</t>
+          <t>Location: Hingalganj, North 24 Parganas, West Bengal</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
       <c r="H23" s="20" t="inlineStr"/>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No fit. AHEAD Initiatives needs a film production agency with cinematography and documentary editing expertise, not an ICT4D company. Skip entirely.</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for documentary film production—a creative media/production service outside Dhwani's core IT and digital solutions expertise; no technology platform, data system, or software development component is involved.</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -1590,34 +1590,34 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>EOI - External Independent Audit : Protecting the Rights of Children by Bu...</t>
+          <t>RFP - for hiring Ambulance vehicle only On Rent</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Regional Centre for Development Cooperation (RCDC)</t>
+          <t>MAMTA Health Institute for Mother and Child (MAMTA)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Location: Odisha</t>
+          <t>Location: Rajasthan</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
       <c r="H24" s="20" t="inlineStr"/>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No action needed. This is a vehicle procurement RFP; Dhwani RIS should not apply. Flag for filtering in future RFP screening to avoid wasting BD time on non-tech tenders.</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>RFP is for ambulance vehicle rental procurement—a physical asset/logistics need with no IT, software, or digital transformation component; entirely outside Dhwani's technology and consulting scope.</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -1637,34 +1637,34 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>RFQ-Outsourced Manpower Services (Housekeeping, MTS, Security &amp; Drivers)</t>
+          <t>EOI - External Independent Audit : Protecting the Rights of Children by Bu...</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI)</t>
+          <t>Regional Centre for Development Cooperation (RCDC)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Location: India</t>
+          <t>Location: Odisha</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
       <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No actionable pitch. RCDC needs a CA audit firm, not a tech vendor. Dhwani could only be relevant if RCDC later needs M&amp;E dashboards or project tracking systems for this or future programs — monitor for follow-up RFPs.</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for external financial audit services from a Chartered Accountant firm — a core accounting/compliance function completely outside Dhwani's IT/software/digital solutions scope.</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -1684,34 +1684,34 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>RFP - for Hiring of a Nukkad Natak Agency for community-based activities u...</t>
+          <t>RFQ-Outsourced Manpower Services (Housekeeping, MTS, Security &amp; Drivers)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>JSI R&amp;T India Foundation (JSI R&amp;T)</t>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>Location: Uttar Pradesh</t>
+          <t>Location: India</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
       <c r="H26" s="20" t="inlineStr"/>
       <c r="I26" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Do not pursue — this is a facilities/HR outsourcing tender, not a technology procurement. Dhwani has no competitive advantage and no product fit.</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFQ is for outsourced non-IT manpower services (housekeeping, MTS, security, drivers) — physical staffing with no software, data system, or digital transformation component; entirely outside Dhwani's IT4D scope.</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -1753,12 +1753,12 @@
       <c r="H27" s="20" t="inlineStr"/>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No action needed. While LEHS's Wadhwani AI program aligns with Dhwani's social sector focus, this specific RFP is for logistics/fleet services, not technology. Monitor LEHS for future digital transformation, HMIS, or AI-enabled M&amp;E RFPs.</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for cab/transportation hiring services, a non-IT procurement category outside Dhwani's core competency in software, data systems, and digital solutions.</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -1778,34 +1778,34 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>RFP - for a Travel Agency</t>
+          <t>RFP - On-Call Taxi Services for Raipur (Chhattisgarh) Local &amp; Outstation T...</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>The Humsafar Trust (HST)</t>
+          <t>Jhpiego</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>Location: India</t>
+          <t>Location: Raipur, Chhattisgarh</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr"/>
       <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Do not pursue. Dhwani does not provide transportation, logistics, or vehicle hire services. This falls outside our ICT4D mandate entirely.</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for on-call taxi/transportation logistics services in Raipur—a physical service delivery requirement with no IT, software, data, or digital transformation component that aligns with Dhwani's tech-for-social-impact portfolio.</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -1825,17 +1825,17 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>RFQ - Study on the Intersection of Megatrends and Child Marriage: Emerging...</t>
+          <t>RFP - for a Travel Agency</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>UNFPA</t>
+          <t>The Humsafar Trust (HST)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -1847,12 +1847,12 @@
       <c r="H29" s="20" t="inlineStr"/>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Do not pursue. This is a travel services RFP, not a technology or data systems engagement. Dhwani has no capability or relevance in travel agency operations.</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>HST is seeking a travel agency vendor for staff/consultant travel booking and logistics—a non-IT procurement that falls entirely outside Dhwani's ICT4D service portfolio.</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -1872,34 +1872,34 @@
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>RFP - An Audio Visual Documentary On The Kalindi River System In The India...</t>
+          <t>RFP - Hiring of Agency to provide Security Guard at Jhpiego State Office, ...</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>AHEAD Initiatives</t>
+          <t>Jhpiego</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>Location: Hingalganj, North 24 Parganas, West Bengal</t>
+          <t>Location: Bhubaneswar, Odisha</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
       <c r="H30" s="20" t="inlineStr"/>
       <c r="I30" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>Not applicable. This is a facilities/HR outsourcing RFP, outside Dhwani's core IT4D, software, and data services portfolio. No technology solution needed.</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFP is for hiring a security guard agency to provide physical security services at an office location—a non-IT, facilities management procurement with no technology, software, data systems, or digital transformation component.</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -1919,34 +1919,34 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>RFP - Development of a Standardised WASH BCC Tool – UL4BC India Package</t>
+          <t>RFQ - Supply, Installation, Commissioning and Handover of Sewerage Pipe la...</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>Deutsche Welthungerhilfe</t>
+          <t>WaterAid India</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Location: India</t>
+          <t>Location: Akarbarnagar Nagar Panchayat, Bhagalpur, Bihar</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
       <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>Enable Claude API for detailed product mapping</t>
+          <t>No tech component to pitch. However, flag WaterAid India as a strategic contact for future M&amp;E, beneficiary tracking, or WASH programme monitoring solutions once their infrastructure project concludes.</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>Based on keyword matching (Claude API not configured)</t>
+          <t>This RFQ is for physical infrastructure (sewerage pipe supply, installation, and biodigester commissioning), not a technology or software solution—outside Dhwani's core IT4D offerings.</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
